--- a/data-manipulation-scripts/sheets-cleanup/sheets/INTERRUPTOR  FAROL 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/INTERRUPTOR  FAROL 03_02.xlsx
@@ -370,7 +370,9 @@
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>70.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -396,7 +398,9 @@
       <c r="C4" s="2">
         <v>1.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>65.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -437,7 +441,7 @@
         <v>1.0</v>
       </c>
       <c r="D7" s="2">
-        <v>65.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="8">
@@ -451,7 +455,7 @@
         <v>1.0</v>
       </c>
       <c r="D8" s="2">
-        <v>65.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="9">
